--- a/pregenerated_results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/pregenerated_results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,10 +537,10 @@
         <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.002</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -564,10 +564,10 @@
         <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>-0.128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="E8" t="n">
-        <v>0.044</v>
+        <v>-0.003</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.001</v>
+        <v>0.043</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008</v>
+        <v>0.064</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>0.034</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.042</v>
+        <v>-0.008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.392</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.029</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.363</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="E12" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.037</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.018</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>-0.054</v>
       </c>
       <c r="D14" t="n">
-        <v>0.038</v>
+        <v>-0.027</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.027</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>-0.401</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>-0.039</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.362</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.007</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>0.024</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>-0.017</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.005</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.113</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.051</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.06200000000000001</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>-0.143</v>
       </c>
       <c r="D20" t="n">
-        <v>0.031</v>
+        <v>-0.044</v>
       </c>
       <c r="E20" t="n">
-        <v>0.046</v>
+        <v>0.09899999999999999</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>-0.024</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.023</v>
+        <v>0.026</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.004</v>
+        <v>-0.001999999999999998</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>0.032</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>0.033</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>0.022</v>
       </c>
       <c r="D23" t="n">
-        <v>0.065</v>
+        <v>0.015</v>
       </c>
       <c r="E23" t="n">
-        <v>0.132</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>0.227</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.042</v>
+        <v>0.022</v>
       </c>
       <c r="E24" t="n">
-        <v>0.101</v>
+        <v>0.205</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.046</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.027</v>
+        <v>-0.002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.027</v>
+        <v>0.044</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>0.077</v>
       </c>
       <c r="D26" t="n">
-        <v>0.019</v>
+        <v>0.031</v>
       </c>
       <c r="E26" t="n">
-        <v>0.109</v>
+        <v>0.046</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>-0.014</v>
       </c>
       <c r="D27" t="n">
-        <v>0.022</v>
+        <v>-0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.205</v>
+        <v>0.012</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>0.197</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03</v>
+        <v>0.064</v>
       </c>
       <c r="E28" t="n">
-        <v>0.362</v>
+        <v>0.133</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>-0.074</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.038</v>
+        <v>-0.04</v>
       </c>
       <c r="E29" t="n">
-        <v>0.363</v>
+        <v>0.034</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.041</v>
       </c>
       <c r="D30" t="n">
-        <v>0.042</v>
+        <v>-0.013</v>
       </c>
       <c r="E30" t="n">
-        <v>0.065</v>
+        <v>0.028</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.013</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.028</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.019</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.057</v>
+        <v>-0.022</v>
       </c>
       <c r="E32" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,18 +1317,45 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>-0.066</v>
       </c>
       <c r="D33" t="n">
-        <v>0.015</v>
+        <v>-0.058</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline_turnover_intention</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,22 +1415,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944053</v>
+        <v>7093.528441237814</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9957648995493169</v>
+        <v>0.9958137312970582</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1325095691671194</v>
+        <v>0.13297606180212</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120527</v>
+        <v>1.68234909115562</v>
       </c>
       <c r="F2" t="n">
-        <v>1.124267686541995</v>
+        <v>1.126973544354103</v>
       </c>
       <c r="G2" t="n">
-        <v>1.678043421071839</v>
+        <v>1.680728130423188</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.588437647332135</v>
+        <v>1.588422507365227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09951383604476918</v>
+        <v>0.099508797515324</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393394112720964</v>
+        <v>1.393388848090303</v>
       </c>
       <c r="E2" t="n">
-        <v>1.783481181943307</v>
+        <v>1.783456166640151</v>
       </c>
       <c r="F2" t="n">
-        <v>2.351594952918417e-57</v>
+        <v>2.327001655312871e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002289543090502453</v>
+        <v>0.002157202703634746</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02004350160191842</v>
+        <v>0.02004412832739043</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03699499817332853</v>
+        <v>-0.03712856691954958</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04157408435433343</v>
+        <v>0.04144297232681907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9090565031154836</v>
+        <v>0.9142950096096353</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02760529193760394</v>
+        <v>-0.02806347567340349</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05181651955565619</v>
+        <v>0.05180741466195352</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1291638040709055</v>
+        <v>-0.1296041425429647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07395322019569761</v>
+        <v>0.07347719119615775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5942060998044847</v>
+        <v>0.5880331806434538</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001979053634585241</v>
+        <v>0.002136000897429307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03523203519821221</v>
+        <v>0.0352189070159448</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06707446645595819</v>
+        <v>-0.06689178842868752</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07103257372512867</v>
+        <v>0.07116379022354614</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9552047922716996</v>
+        <v>0.9516385362649579</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03340001985125003</v>
+        <v>0.03303202308651727</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03286258508177218</v>
+        <v>0.03286800426819424</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0310094633479067</v>
+        <v>-0.03138808152285223</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09780950305040677</v>
+        <v>0.09745212769588676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3094608416342971</v>
+        <v>0.3149015555617197</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01514663535578087</v>
+        <v>-0.01521228708610778</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03537760492293865</v>
+        <v>0.03536389523671278</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08448546686402754</v>
+        <v>-0.0845242481031124</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0541921961524658</v>
+        <v>0.05409967393089685</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6685478054594496</v>
+        <v>0.6670760911481439</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01391452100577118</v>
+        <v>-0.01369113270818714</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03582624135777854</v>
+        <v>0.03583749565076259</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08413266376845648</v>
+        <v>-0.08393133347979263</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05630362175691413</v>
+        <v>0.05654906806341835</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6977281223699656</v>
+        <v>0.7024363340113144</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02606854715545236</v>
+        <v>-0.02619917626172894</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03445174256130681</v>
+        <v>0.03445373577537432</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09359272178025943</v>
+        <v>-0.09372725751432179</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04145562746935471</v>
+        <v>0.04132890499086392</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4492485122499706</v>
+        <v>0.4470058874486467</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1243555105431011</v>
+        <v>-0.1242064437800988</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05548145045815717</v>
+        <v>0.0554841752501268</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2330971552511324</v>
+        <v>-0.232953428982256</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01561386583506978</v>
+        <v>-0.01545945857794168</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02500089100745381</v>
+        <v>0.0251824600613936</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07368505338474868</v>
+        <v>0.07320420542333145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05628990533964612</v>
+        <v>0.0562868822852635</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03664113377412659</v>
+        <v>-0.03711605665783059</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1840112405436239</v>
+        <v>0.1835244675044935</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1905249193656604</v>
+        <v>0.1934107016225529</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.06039226355577043</v>
+        <v>-0.06076403853532319</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06009378790448146</v>
+        <v>0.06002138315034811</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1781739235431428</v>
+        <v>-0.1784037878122847</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05738939643160196</v>
+        <v>0.05687571074163836</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3149128220217319</v>
+        <v>0.311359656851861</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03918292931079817</v>
+        <v>-0.03935267962244705</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05709010836228823</v>
+        <v>0.05702989918185156</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1510774855743721</v>
+        <v>-0.1511292280608264</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07271162695277572</v>
+        <v>0.07242386881593231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4925019956822237</v>
+        <v>0.4901715914374869</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08961924675638717</v>
+        <v>-0.08994407386175061</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05597301997478087</v>
+        <v>0.05595151464980271</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1993243500128987</v>
+        <v>-0.1996070274558291</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02008585650012439</v>
+        <v>0.01971887973232792</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1093514311924692</v>
+        <v>0.1079368395669108</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07971063832368429</v>
+        <v>-0.07972002010245757</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05486702563238852</v>
+        <v>0.05482862722193878</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1872480325020018</v>
+        <v>-0.18718215477923</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02782675585463319</v>
+        <v>0.02774211457431483</v>
       </c>
       <c r="F15" t="n">
-        <v>0.146280185467767</v>
+        <v>0.1459503711242125</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07536173463392262</v>
+        <v>-0.07580821482423751</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05394309282729035</v>
+        <v>0.05391836373954744</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1810882537901126</v>
+        <v>-0.1814862658590809</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03036478452226737</v>
+        <v>0.02986983621060586</v>
       </c>
       <c r="F16" t="n">
-        <v>0.16239554370749</v>
+        <v>0.1597296574439617</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007508945504431017</v>
+        <v>-0.007958708481944505</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05689726041689017</v>
+        <v>0.0568658590176258</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1190255267405322</v>
+        <v>-0.1194137441064233</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1040076357316701</v>
+        <v>0.1034963271425343</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8950050450910978</v>
+        <v>0.888694889582647</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02702123264755605</v>
+        <v>-0.02674600637292562</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05498884081168755</v>
+        <v>0.05495082849883484</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1347973801900699</v>
+        <v>-0.1344476511512791</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08075491489495783</v>
+        <v>0.08095563840542787</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6231472128909767</v>
+        <v>0.6264523959201846</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08375751060329222</v>
+        <v>-0.08417048724369858</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05360990234935124</v>
+        <v>0.0535657530627311</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1888309884227299</v>
+        <v>-0.1891574340514176</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02131596721614544</v>
+        <v>0.02081645956402046</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1182052092143456</v>
+        <v>0.1161016281223214</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1311358803541575</v>
+        <v>-0.1315545875635715</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05406282801340159</v>
+        <v>0.0540266386255847</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2370970761628077</v>
+        <v>-0.2374448534754781</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02517468454550724</v>
+        <v>-0.02566432165166492</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01528225980615037</v>
+        <v>0.01489200108264306</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1241875106822867</v>
+        <v>-0.1243413906692295</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05616362862747459</v>
+        <v>0.0561830384698432</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2342662000332196</v>
+        <v>-0.2344581226121505</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01410882133135373</v>
+        <v>-0.01422465872630849</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0270238451880946</v>
+        <v>0.02688742972151396</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07269691488818499</v>
+        <v>-0.07290986245855964</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05654139166683255</v>
+        <v>0.05651076265826963</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1835160061909499</v>
+        <v>-0.1836689220076591</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03812217641457995</v>
+        <v>0.0378491970905398</v>
       </c>
       <c r="F22" t="n">
-        <v>0.198537607679667</v>
+        <v>0.1969832133925163</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01550704881921866</v>
+        <v>-0.01550122276689227</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05396301665233486</v>
+        <v>0.05392880208198832</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1212726179549302</v>
+        <v>-0.1211997325769781</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09025852031649287</v>
+        <v>0.09019728704319352</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7738333321942779</v>
+        <v>0.7737764608404213</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01712641609733917</v>
+        <v>-0.01736702286559939</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04898189205297218</v>
+        <v>0.04895754327588756</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1131291604157933</v>
+        <v>-0.1133220444579001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.078876328221115</v>
+        <v>0.07858799872670132</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7266029520031178</v>
+        <v>0.722787075588749</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01900783443856897</v>
+        <v>0.01900414985650928</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02561343601916738</v>
+        <v>0.02562283647390881</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03119357767932007</v>
+        <v>-0.03121568681411126</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06920924655645801</v>
+        <v>0.06922398652712981</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4580243001316253</v>
+        <v>0.4582764034316498</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.01141783923973176</v>
+        <v>-0.01136511239972227</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03075125430929366</v>
+        <v>0.03076545132329944</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07168919016537946</v>
+        <v>-0.07166428896150931</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04885351168591594</v>
+        <v>0.04893406416206476</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7104165557438002</v>
+        <v>0.7118210062148206</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008263771382752912</v>
+        <v>0.008288872114817955</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03117627639559385</v>
+        <v>0.03118021288371116</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.05284060752467724</v>
+        <v>-0.0528232221675477</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06936815029018306</v>
+        <v>0.06940096639718361</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7909586063851295</v>
+        <v>0.7903643050508876</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.04411323392421414</v>
+        <v>0.04441792109265477</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03148338007871246</v>
+        <v>0.03147225308209889</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.01759305714164808</v>
+        <v>-0.01726656146058876</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1058195249900764</v>
+        <v>0.1061024036458983</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1611664122763742</v>
+        <v>0.1581455893971986</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0109349089395617</v>
+        <v>-0.01111026890206917</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03231638714325727</v>
+        <v>0.03230457849540543</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07427386385079919</v>
+        <v>-0.07442607928881094</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05240404597167579</v>
+        <v>0.05220554148467262</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7350840751185992</v>
+        <v>0.7309046284390832</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2300267851900341</v>
+        <v>0.2303472064753822</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0427568726402331</v>
+        <v>0.04274619914367982</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1462248547236112</v>
+        <v>0.1465661956777928</v>
       </c>
       <c r="E30" t="n">
-        <v>0.313828715656457</v>
+        <v>0.3141282172729715</v>
       </c>
       <c r="F30" t="n">
-        <v>7.453607464503609e-08</v>
+        <v>7.096210791271912e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2216,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.009570099507611824</v>
+        <v>0.009295972736054529</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02352815839717277</v>
+        <v>0.02351946149446091</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.03654424357340044</v>
+        <v>-0.03680132472886545</v>
       </c>
       <c r="E31" t="n">
-        <v>0.05568444258862409</v>
+        <v>0.05539327020097451</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6841909551554408</v>
+        <v>0.6926613581382861</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0008959807646594254</v>
+        <v>0.4907763416057432</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001756049857289153</v>
+        <v>0.01020349621388541</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004337775240002869</v>
+        <v>0.470777856510137</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002545813710684017</v>
+        <v>0.5107748267013493</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6098937492520379</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001002562195601323</v>
+        <v>-0.000884789653136881</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001411716497337632</v>
+        <v>0.001755881165775701</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003769475686764117</v>
+        <v>-0.004326253499189459</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001764351295561471</v>
+        <v>0.002556674192915697</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4775971888880642</v>
+        <v>0.6143311968318028</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.00770111188713586</v>
+        <v>-0.001023762880892494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00456379741513831</v>
+        <v>0.001412550988754018</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.01664599045354394</v>
+        <v>-0.003792311945176813</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00124376667927222</v>
+        <v>0.001744786183391825</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09151972193448007</v>
+        <v>0.4685982250511592</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001336822150411826</v>
+        <v>-0.00768490996481686</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001449434599930921</v>
+        <v>0.004562970024586886</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.001504017463399001</v>
+        <v>-0.016628166875543</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004177661764222653</v>
+        <v>0.00125834694590928</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3563690132001174</v>
+        <v>0.09214489260396783</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4906715993267194</v>
+        <v>0.001323773742398874</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01020038761332365</v>
+        <v>0.00144966666492717</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4706792069762565</v>
+        <v>-0.001517520710446673</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5106639916771822</v>
+        <v>0.004165068195244421</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.3611598015227343</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2343,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.820303044554362</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.5099234395092709</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>3.1870773524043e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02464939576457222</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033998</v>
+        <v>0.1003099681595393</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.8058894933269589</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2249663577428585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2337176582603366</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069162</v>
+        <v>0.3357703370011802</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8191373674885463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173402651392118</v>
+        <v>0.1734167828528216</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.317989576597441e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.03652125765996373</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.191713295917962</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.8489178549322618</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2789564326928405</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133385</v>
+        <v>0.1901139906226964</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.1422913540098482</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1068531552827689</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.1953287956048302</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5843495250374446</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8765772051307454</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.1697332036095893</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.411578475116274e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.04447986866030674</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.260451332255926</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.8643967854929906</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.2727472209256583</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2791278961561439</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3284995130487413</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.07889678868393089</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2596148796948621</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7612045862333772</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.04019393041481644</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743774</v>
+        <v>0.25742040413283</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8759217249006986</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.04910228165084279</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.2612561015991013</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375534</v>
+        <v>0.8509182551619308</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1160743543422991</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2571236264961844</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984086</v>
+        <v>0.6516767631412983</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.002512421030226103</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2386078717504868</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.9915988316144652</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.1088094847883377</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.2546184298925979</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.6691292855457318</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1371054629493663</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.2637238215346589</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6031453060319987</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02469784288290743</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.2529058254775156</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.922205230617394</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.06845683158478723</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.2673011584513997</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.7978707191500395</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.2086621675742924</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.2442815662419171</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.3930013184626149</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362028</v>
+        <v>-0.1754067081881008</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.2700541998112385</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.5159996811704795</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.5004384224930731</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2870894861894643</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.0813083992692025</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9379041483579631</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483430409733375</v>
+        <v>0.1484949273354128</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.683009814405851e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5776000776467407</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1143336799033597</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.374815955439317e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2357452695510325</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377481</v>
+        <v>0.1505208025229892</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757815</v>
+        <v>0.117302442329191</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04479861183336156</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.1611783258696414</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7810550458340697</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.07528727625378256</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.1614983128820297</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6410866959853148</v>
       </c>
     </row>
     <row r="29">
@@ -2807,13 +2834,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09387617646092143</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543340718197334</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.5430110331238933</v>
       </c>
     </row>
     <row r="30">
@@ -2823,77 +2850,93 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>0.2256479096144982</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.1147189874002692</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.04918757099961305</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>0.04715208655231704</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.04889616403699383</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.3348800057442067</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>-0.004826402612991638</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.008314480096142966</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.5615898992578163</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>-0.002469929930368315</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.00713076369058149</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.7290596823423183</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>num_direct_reports</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.003793322855986123</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.02223202690000052</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.8645192309060558</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>tot_span_of_control</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.006335499136474494</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.006871422968197173</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+      <c r="B35" t="n">
+        <v>0.006311908087997973</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.006867343796543264</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3580331856516401</v>
       </c>
     </row>
   </sheetData>
